--- a/application/plugins/Reports_stock_movements/Reports_stock_movements.xlsx
+++ b/application/plugins/Reports_stock_movements/Reports_stock_movements.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
   <si>
     <t>Всего</t>
   </si>
@@ -137,12 +137,48 @@
   </si>
   <si>
     <t>{$v-&gt;input-&gt;include_vat}</t>
+  </si>
+  <si>
+    <t>Подробный отчет</t>
+  </si>
+  <si>
+    <t>{$v-&gt;rows[]-&gt;group_by}</t>
+  </si>
+  <si>
+    <t>{$v-&gt;rows[]-&gt;sell_qty}</t>
+  </si>
+  <si>
+    <t>{$v-&gt;rows[]-&gt;sell_sum}</t>
+  </si>
+  <si>
+    <t>{$v-&gt;rows[]-&gt;stock_fqty}</t>
+  </si>
+  <si>
+    <t>{$v-&gt;rows[]-&gt;stock_fsum}</t>
+  </si>
+  <si>
+    <t>{$v-&gt;rows[]-&gt;stock_isum}</t>
+  </si>
+  <si>
+    <t>{$v-&gt;rows[]-&gt;stock_iqty}</t>
+  </si>
+  <si>
+    <t>Товар</t>
+  </si>
+  <si>
+    <t>{$v-&gt;rows[]-&gt;buy_sum}</t>
+  </si>
+  <si>
+    <t>{$v-&gt;rows[]-&gt;buy_qty}</t>
+  </si>
+  <si>
+    <t>{$v-&gt;rows[]-&gt;_product_code}  {$v-&gt;rows[]-&gt;ru}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -194,30 +230,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor rgb="FFD0EAF0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
+        <fgColor rgb="FFEEEEEE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
+        <fgColor rgb="FFB6B6B6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor rgb="FFA0D2E0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -287,21 +323,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -376,7 +397,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -394,7 +415,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -406,15 +427,92 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -425,40 +523,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -466,46 +570,79 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Процентный" xfId="1" builtinId="5"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFA0D2E0"/>
+      <color rgb="FFB6B6B6"/>
+      <color rgb="FFEEEEEE"/>
+      <color rgb="FFD0EAF0"/>
+      <color rgb="FF7AC1D4"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -518,9 +655,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -558,7 +695,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -630,7 +767,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -804,213 +941,219 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="9" width="10" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" customWidth="1"/>
+    <col min="3" max="10" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="26"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="14"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="12" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="12" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="12" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="12" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
         <v>33</v>
       </c>
       <c r="B7" s="23"/>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>35</v>
       </c>
       <c r="B8" s="23"/>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="12" t="s">
+      <c r="B9" s="23"/>
+      <c r="C9" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:9" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="14" t="s">
+    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:10" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
       <c r="I11" s="16"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
+      <c r="J11" s="17"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="25"/>
+      <c r="C12" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="26"/>
+      <c r="E12" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="26"/>
+      <c r="G12" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="26"/>
+      <c r="I12" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="18"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
-      <c r="B13" s="5" t="s">
+      <c r="J12" s="27"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="J13" s="31" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="21"/>
+      <c r="C14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="I14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="J14" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="19"/>
+      <c r="C15" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="D15" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="F15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="G15" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="H15" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="I15" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="J15" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1019,25 +1162,146 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-      <c r="I16" s="3"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:10" ht="24" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="17"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="35"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="28"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="I21" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="1"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
+  <mergeCells count="24">
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A12:B13"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
